--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_27.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="66">
   <si>
     <t>Result</t>
   </si>
@@ -231,6 +231,18 @@
   </si>
   <si>
     <t>Thu Aug 27 19:32:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:55:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 15:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 15:10:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 15:18:29 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2500,7 +2512,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_27.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="70">
   <si>
     <t>Result</t>
   </si>
@@ -243,6 +243,18 @@
   </si>
   <si>
     <t>Tue Oct 20 15:18:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:47:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:52:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:54:22 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2512,7 +2524,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
